--- a/results/mean_platt5d.xlsx
+++ b/results/mean_platt5d.xlsx
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.03815143084033142</v>
+        <v>0.03876631986076129</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.05192216674822492</v>
+        <v>0.05385701399555246</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.7233485650541269</v>
+        <v>0.7309388127508656</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1408185877954547</v>
+        <v>0.1411503608120991</v>
       </c>
     </row>
     <row r="6">
@@ -586,16 +586,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.03713575151730068</v>
+        <v>0.04032069602814083</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.05651618861847627</v>
+        <v>0.05479732532320283</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6836044992332401</v>
+        <v>0.6840751268525903</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1420298580945667</v>
+        <v>0.1426340927511489</v>
       </c>
     </row>
     <row r="8">
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="C17" s="1" t="n">
-        <v>0.0492646869527586</v>
+        <v>0.05196436155638658</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.05549378139223062</v>
+        <v>0.06897455878346505</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.7653984125051525</v>
+        <v>0.764948239864317</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.1418113364972837</v>
+        <v>0.1438814241622837</v>
       </c>
     </row>
     <row r="18">
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>0.04643147019933731</v>
+        <v>0.05170549661122005</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>0.06691454163421917</v>
+        <v>0.06076696425510595</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.7211072556895094</v>
+        <v>0.7218136257061301</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.1467746144518285</v>
+        <v>0.1477002310877703</v>
       </c>
     </row>
     <row r="20">
